--- a/docs/files/exports/combined-combined-client-questionnaire.xlsx
+++ b/docs/files/exports/combined-combined-client-questionnaire.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Combined Web + App Client Questionnaire</t>
+          <t>Client Discovery Questionnaire</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4,233 words</t>
+          <t>4,193 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Combined Web + App Client Questionnaire All-in-one client discovery questionnaire. Send this when a client needs both a website and a mobile application, or when you want a single intake form to qualify both scopes. Scop...</t>
+          <t>Client Discovery Questionnaire All-in-one structured client questionnaire for scoping both Website and Mobile Application projects in a single intake session. Covers business overview, technical requirements, design, fea...</t>
         </is>
       </c>
     </row>
